--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1885,6 +1885,218 @@
       <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/76177402</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136537672</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Z346 Fjällsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>568071</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7082649</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136537672</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136545922</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Z346 Fjällsjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567982</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7082889</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136545922</t>
         </is>
       </c>
     </row>
@@ -1900,6 +2112,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Johanna Björkman</t>
+          <t>Johanna Björkman, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johanna Björkman, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Johanna Björkman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69142-2021 artfynd.xlsx
+++ b/artfynd/A 69142-2021 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>136537672</v>
       </c>
       <c r="B12" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136545922</v>
       </c>
       <c r="B13" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
